--- a/3th course/МИЭП/lab5.xlsx
+++ b/3th course/МИЭП/lab5.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bajsh\Desktop\university\3th course\МИЭП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE2BAE3A-48B6-4948-9291-F9F1B9DBADFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF7652D-4C9E-44C2-B46C-5018048BD7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{5C872C3F-F682-9749-9BA9-9E89B5099812}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C872C3F-F682-9749-9BA9-9E89B5099812}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>№</t>
   </si>
@@ -224,12 +202,83 @@
       <t xml:space="preserve"> Y =</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(X </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> X) </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>−1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> X </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Y =</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -242,11 +291,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -269,6 +320,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -277,6 +329,14 @@
       <color theme="1"/>
       <name val="Aptos Narrow (Основной текст)"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -460,9 +520,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -520,6 +577,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -855,19 +915,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAE8F280-4239-784A-A99A-DF7CF243BA62}">
   <dimension ref="A1:L63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.375" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="61" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="60.95" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -884,7 +944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -914,7 +974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -940,7 +1000,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="1">
         <f>A3+1</f>
         <v>2</v>
@@ -969,7 +1029,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A32" si="0">A4+1</f>
         <v>3</v>
@@ -1000,7 +1060,7 @@
       </c>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="16.5" thickBot="1">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1033,7 +1093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1051,7 +1111,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1068,14 +1128,14 @@
       <c r="E8" s="3">
         <v>143</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1108,7 +1168,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1128,7 +1188,7 @@
       <c r="G10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <v>0.94504260203988932</v>
       </c>
       <c r="I10" s="9">
@@ -1143,7 +1203,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1163,7 +1223,7 @@
       <c r="G11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <v>0.75633192469615929</v>
       </c>
       <c r="I11" s="9">
@@ -1176,7 +1236,7 @@
       </c>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1196,7 +1256,7 @@
       <c r="G12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>0.92237144000000004</v>
       </c>
       <c r="I12" s="9">
@@ -1209,7 +1269,7 @@
       </c>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1229,7 +1289,7 @@
       <c r="G13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>0.70108530599999996</v>
       </c>
       <c r="I13" s="9">
@@ -1242,7 +1302,7 @@
       </c>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1260,7 +1320,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1278,7 +1338,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1296,7 +1356,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1314,7 +1374,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1332,7 +1392,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1350,7 +1410,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1368,7 +1428,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1386,7 +1446,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1404,7 +1464,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1422,7 +1482,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1440,7 +1500,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1458,7 +1518,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1476,7 +1536,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1494,7 +1554,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1512,7 +1572,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1530,7 +1590,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1548,7 +1608,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <f>A30+1</f>
         <v>29</v>
@@ -1566,7 +1626,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1584,468 +1644,517 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="13">
-        <v>1</v>
-      </c>
-      <c r="C34" s="14">
+    <row r="34" spans="2:12">
+      <c r="B34" s="12">
+        <v>1</v>
+      </c>
+      <c r="C34" s="13">
         <v>44502</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="14">
         <v>153</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="21">
         <v>6429</v>
       </c>
-      <c r="J34" s="25"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="27"/>
-    </row>
-    <row r="35" spans="2:12" ht="19" x14ac:dyDescent="0.2">
-      <c r="B35" s="16">
-        <v>1</v>
-      </c>
-      <c r="C35" s="17">
+      <c r="J34" s="24">
+        <f t="array" ref="J34:L36">MMULT(TRANSPOSE(B34:D63), B34:D63)</f>
+        <v>30</v>
+      </c>
+      <c r="K34" s="25">
+        <v>1521061</v>
+      </c>
+      <c r="L34" s="26">
+        <v>5270</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" ht="18.75">
+      <c r="B35" s="15">
+        <v>1</v>
+      </c>
+      <c r="C35" s="16">
         <v>38390</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="17">
         <v>174</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="22">
         <v>5265</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
       </c>
-      <c r="J35" s="28"/>
-      <c r="L35" s="30"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="16">
-        <v>1</v>
-      </c>
-      <c r="C36" s="17">
+      <c r="J35" s="27">
+        <v>1521061</v>
+      </c>
+      <c r="K35">
+        <v>87356501177</v>
+      </c>
+      <c r="L35" s="29">
+        <v>303217247</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="15">
+        <v>1</v>
+      </c>
+      <c r="C36" s="16">
         <v>68857</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="17">
         <v>241</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="22">
         <v>8027</v>
       </c>
-      <c r="J36" s="31"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="33"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="16">
-        <v>1</v>
-      </c>
-      <c r="C37" s="17">
+      <c r="J36" s="30">
+        <v>5270</v>
+      </c>
+      <c r="K36" s="31">
+        <v>303217247</v>
+      </c>
+      <c r="L36" s="32">
+        <v>1075332</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" s="15">
+        <v>1</v>
+      </c>
+      <c r="C37" s="16">
         <v>31650</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="17">
         <v>122</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="22">
         <v>3590</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="16">
-        <v>1</v>
-      </c>
-      <c r="C38" s="17">
+    <row r="38" spans="2:12">
+      <c r="B38" s="15">
+        <v>1</v>
+      </c>
+      <c r="C38" s="16">
         <v>26353</v>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="17">
         <v>88</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="22">
         <v>2962</v>
       </c>
-      <c r="J38" s="25" t="e" cm="1">
-        <f t="array" ref="J38">MINVERSE(J34:L36)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K38" s="26"/>
-      <c r="L38" s="27"/>
-    </row>
-    <row r="39" spans="2:12" ht="19" x14ac:dyDescent="0.2">
-      <c r="B39" s="16">
-        <v>1</v>
-      </c>
-      <c r="C39" s="17">
+      <c r="J38" s="24">
+        <f t="array" ref="J38:L40">MINVERSE(J34:L36)</f>
+        <v>0.28481569242061167</v>
+      </c>
+      <c r="K38" s="25">
+        <v>-5.3767436590376639E-6</v>
+      </c>
+      <c r="L38" s="26">
+        <v>1.2028165353721898E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" ht="18.75">
+      <c r="B39" s="15">
+        <v>1</v>
+      </c>
+      <c r="C39" s="16">
         <v>43109</v>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="17">
         <v>143</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="22">
         <v>5601</v>
       </c>
       <c r="I39" t="s">
         <v>23</v>
       </c>
-      <c r="J39" s="28"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="30"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="16">
-        <v>1</v>
-      </c>
-      <c r="C40" s="17">
+      <c r="J39" s="27">
+        <v>-5.3767436590376978E-6</v>
+      </c>
+      <c r="K39" s="28">
+        <v>6.400992033967554E-10</v>
+      </c>
+      <c r="L39" s="29">
+        <v>-1.5414186425934374E-7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
+      <c r="B40" s="15">
+        <v>1</v>
+      </c>
+      <c r="C40" s="16">
         <v>40878</v>
       </c>
-      <c r="D40" s="18">
+      <c r="D40" s="17">
         <v>132</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="22">
         <v>5603</v>
       </c>
-      <c r="J40" s="31"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="33"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="16">
-        <v>1</v>
-      </c>
-      <c r="C41" s="17">
+      <c r="J40" s="30">
+        <v>1.2028165353722753E-4</v>
+      </c>
+      <c r="K40" s="31">
+        <v>-1.5414186425934387E-7</v>
+      </c>
+      <c r="L40" s="32">
+        <v>4.3804692331321642E-5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41" s="15">
+        <v>1</v>
+      </c>
+      <c r="C41" s="16">
         <v>35776</v>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="17">
         <v>133</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="22">
         <v>4778</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="16">
-        <v>1</v>
-      </c>
-      <c r="C42" s="17">
+    <row r="42" spans="2:12">
+      <c r="B42" s="15">
+        <v>1</v>
+      </c>
+      <c r="C42" s="16">
         <v>37539</v>
       </c>
-      <c r="D42" s="18">
+      <c r="D42" s="17">
         <v>116</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="22">
         <v>4014</v>
       </c>
-      <c r="J42" s="34" cm="1">
+      <c r="J42" s="33">
         <f t="array" ref="J42:J44">MMULT(TRANSPOSE(B34:D63), G34:G63)</f>
         <v>204152</v>
       </c>
     </row>
-    <row r="43" spans="2:12" ht="19" x14ac:dyDescent="0.2">
-      <c r="B43" s="16">
-        <v>1</v>
-      </c>
-      <c r="C43" s="17">
+    <row r="43" spans="2:12" ht="18.75">
+      <c r="B43" s="15">
+        <v>1</v>
+      </c>
+      <c r="C43" s="16">
         <v>54230</v>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="17">
         <v>159</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="22">
         <v>6008</v>
       </c>
       <c r="I43" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="35">
+      <c r="J43" s="34">
         <v>11789069952</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="16">
-        <v>1</v>
-      </c>
-      <c r="C44" s="17">
+    <row r="44" spans="2:12">
+      <c r="B44" s="15">
+        <v>1</v>
+      </c>
+      <c r="C44" s="16">
         <v>50117</v>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="17">
         <v>189</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="22">
         <v>6190</v>
       </c>
-      <c r="J44" s="36">
+      <c r="J44" s="35">
         <v>41228341</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45" s="16">
-        <v>1</v>
-      </c>
-      <c r="C45" s="17">
+    <row r="45" spans="2:12">
+      <c r="B45" s="15">
+        <v>1</v>
+      </c>
+      <c r="C45" s="16">
         <v>55941</v>
       </c>
-      <c r="D45" s="18">
+      <c r="D45" s="17">
         <v>159</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="22">
         <v>7515</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46" s="16">
-        <v>1</v>
-      </c>
-      <c r="C46" s="17">
+    <row r="46" spans="2:12">
+      <c r="B46" s="15">
+        <v>1</v>
+      </c>
+      <c r="C46" s="16">
         <v>29658</v>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="17">
         <v>85</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="22">
         <v>3796</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47" s="16">
-        <v>1</v>
-      </c>
-      <c r="C47" s="17">
+      <c r="J46" s="33">
+        <f t="array" ref="J46:J48">MMULT(J38:L40, J42:J44)</f>
+        <v>-282.1008432384242</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" ht="18">
+      <c r="B47" s="15">
+        <v>1</v>
+      </c>
+      <c r="C47" s="16">
         <v>52303</v>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="17">
         <v>144</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="22">
         <v>7632</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="16">
-        <v>1</v>
-      </c>
-      <c r="C48" s="17">
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="34">
+        <v>9.3487971524025326E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
+      <c r="B48" s="15">
+        <v>1</v>
+      </c>
+      <c r="C48" s="16">
         <v>19397</v>
       </c>
-      <c r="D48" s="18">
+      <c r="D48" s="17">
         <v>105</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="22">
         <v>2907</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J48" s="35">
+        <v>13.361312683651931</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="16">
-        <v>1</v>
-      </c>
-      <c r="C49" s="17">
+      <c r="B49" s="15">
+        <v>1</v>
+      </c>
+      <c r="C49" s="16">
         <v>61771</v>
       </c>
-      <c r="D49" s="18">
+      <c r="D49" s="17">
         <v>168</v>
       </c>
       <c r="F49" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="23">
+      <c r="G49" s="22">
         <v>7484</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="16">
-        <v>1</v>
-      </c>
-      <c r="C50" s="17">
+    <row r="50" spans="1:7">
+      <c r="B50" s="15">
+        <v>1</v>
+      </c>
+      <c r="C50" s="16">
         <v>71384</v>
       </c>
-      <c r="D50" s="18">
+      <c r="D50" s="17">
         <v>241</v>
       </c>
-      <c r="G50" s="23">
+      <c r="G50" s="22">
         <v>9743</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="16">
-        <v>1</v>
-      </c>
-      <c r="C51" s="17">
+    <row r="51" spans="1:7">
+      <c r="B51" s="15">
+        <v>1</v>
+      </c>
+      <c r="C51" s="16">
         <v>72981</v>
       </c>
-      <c r="D51" s="18">
+      <c r="D51" s="17">
         <v>263</v>
       </c>
-      <c r="G51" s="23">
+      <c r="G51" s="22">
         <v>10652</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B52" s="16">
-        <v>1</v>
-      </c>
-      <c r="C52" s="17">
+    <row r="52" spans="1:7">
+      <c r="B52" s="15">
+        <v>1</v>
+      </c>
+      <c r="C52" s="16">
         <v>98853</v>
       </c>
-      <c r="D52" s="18">
+      <c r="D52" s="17">
         <v>417</v>
       </c>
-      <c r="G52" s="23">
+      <c r="G52" s="22">
         <v>13424</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="16">
-        <v>1</v>
-      </c>
-      <c r="C53" s="17">
+    <row r="53" spans="1:7">
+      <c r="B53" s="15">
+        <v>1</v>
+      </c>
+      <c r="C53" s="16">
         <v>48372</v>
       </c>
-      <c r="D53" s="18">
+      <c r="D53" s="17">
         <v>175</v>
       </c>
-      <c r="G53" s="23">
+      <c r="G53" s="22">
         <v>6656</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B54" s="16">
-        <v>1</v>
-      </c>
-      <c r="C54" s="17">
+    <row r="54" spans="1:7">
+      <c r="B54" s="15">
+        <v>1</v>
+      </c>
+      <c r="C54" s="16">
         <v>50514</v>
       </c>
-      <c r="D54" s="18">
+      <c r="D54" s="17">
         <v>170</v>
       </c>
-      <c r="G54" s="23">
+      <c r="G54" s="22">
         <v>5657</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B55" s="16">
-        <v>1</v>
-      </c>
-      <c r="C55" s="17">
+    <row r="55" spans="1:7">
+      <c r="B55" s="15">
+        <v>1</v>
+      </c>
+      <c r="C55" s="16">
         <v>67027</v>
       </c>
-      <c r="D55" s="18">
+      <c r="D55" s="17">
         <v>227</v>
       </c>
-      <c r="G55" s="23">
+      <c r="G55" s="22">
         <v>9651</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B56" s="16">
-        <v>1</v>
-      </c>
-      <c r="C56" s="17">
+    <row r="56" spans="1:7">
+      <c r="B56" s="15">
+        <v>1</v>
+      </c>
+      <c r="C56" s="16">
         <v>73278</v>
       </c>
-      <c r="D56" s="18">
+      <c r="D56" s="17">
         <v>281</v>
       </c>
-      <c r="G56" s="23">
+      <c r="G56" s="22">
         <v>9803</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B57" s="16">
-        <v>1</v>
-      </c>
-      <c r="C57" s="17">
+    <row r="57" spans="1:7">
+      <c r="B57" s="15">
+        <v>1</v>
+      </c>
+      <c r="C57" s="16">
         <v>39549</v>
       </c>
-      <c r="D57" s="18">
+      <c r="D57" s="17">
         <v>150</v>
       </c>
-      <c r="G57" s="23">
+      <c r="G57" s="22">
         <v>5425</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B58" s="16">
-        <v>1</v>
-      </c>
-      <c r="C58" s="17">
+    <row r="58" spans="1:7">
+      <c r="B58" s="15">
+        <v>1</v>
+      </c>
+      <c r="C58" s="16">
         <v>28495</v>
       </c>
-      <c r="D58" s="18">
+      <c r="D58" s="17">
         <v>98</v>
       </c>
-      <c r="G58" s="23">
+      <c r="G58" s="22">
         <v>3784</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B59" s="16">
-        <v>1</v>
-      </c>
-      <c r="C59" s="17">
+    <row r="59" spans="1:7">
+      <c r="B59" s="15">
+        <v>1</v>
+      </c>
+      <c r="C59" s="16">
         <v>88151</v>
       </c>
-      <c r="D59" s="18">
+      <c r="D59" s="17">
         <v>258</v>
       </c>
-      <c r="G59" s="23">
+      <c r="G59" s="22">
         <v>11913</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="16">
-        <v>1</v>
-      </c>
-      <c r="C60" s="17">
+    <row r="60" spans="1:7">
+      <c r="B60" s="15">
+        <v>1</v>
+      </c>
+      <c r="C60" s="16">
         <v>63565</v>
       </c>
-      <c r="D60" s="18">
+      <c r="D60" s="17">
         <v>229</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="22">
         <v>9867</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B61" s="16">
-        <v>1</v>
-      </c>
-      <c r="C61" s="17">
+    <row r="61" spans="1:7">
+      <c r="B61" s="15">
+        <v>1</v>
+      </c>
+      <c r="C61" s="16">
         <v>31248</v>
       </c>
-      <c r="D61" s="18">
+      <c r="D61" s="17">
         <v>112</v>
       </c>
-      <c r="G61" s="23">
+      <c r="G61" s="22">
         <v>4359</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B62" s="16">
-        <v>1</v>
-      </c>
-      <c r="C62" s="17">
+    <row r="62" spans="1:7">
+      <c r="B62" s="15">
+        <v>1</v>
+      </c>
+      <c r="C62" s="16">
         <v>52097</v>
       </c>
-      <c r="D62" s="18">
+      <c r="D62" s="17">
         <v>226</v>
       </c>
-      <c r="G62" s="23">
+      <c r="G62" s="22">
         <v>10506</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B63" s="19">
-        <v>1</v>
-      </c>
-      <c r="C63" s="20">
+    <row r="63" spans="1:7">
+      <c r="B63" s="18">
+        <v>1</v>
+      </c>
+      <c r="C63" s="19">
         <v>45076</v>
       </c>
-      <c r="D63" s="21">
+      <c r="D63" s="20">
         <v>112</v>
       </c>
-      <c r="G63" s="24">
+      <c r="G63" s="23">
         <v>4911</v>
       </c>
     </row>

--- a/3th course/МИЭП/lab5.xlsx
+++ b/3th course/МИЭП/lab5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE2BAE3A-48B6-4948-9291-F9F1B9DBADFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7675F0-BFBE-BD40-86E0-CD4AEEECAACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{5C872C3F-F682-9749-9BA9-9E89B5099812}"/>
   </bookViews>
@@ -1597,9 +1597,16 @@
       <c r="G34" s="22">
         <v>6429</v>
       </c>
-      <c r="J34" s="25"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="27"/>
+      <c r="J34" s="25" cm="1">
+        <f t="array" ref="J34:L36">MMULT(TRANSPOSE(B34:D63), B34:D63)</f>
+        <v>30</v>
+      </c>
+      <c r="K34" s="26">
+        <v>1521061</v>
+      </c>
+      <c r="L34" s="27">
+        <v>5270</v>
+      </c>
     </row>
     <row r="35" spans="2:12" ht="19" x14ac:dyDescent="0.2">
       <c r="B35" s="16">
@@ -1617,8 +1624,15 @@
       <c r="I35" t="s">
         <v>22</v>
       </c>
-      <c r="J35" s="28"/>
-      <c r="L35" s="30"/>
+      <c r="J35" s="28">
+        <v>1521061</v>
+      </c>
+      <c r="K35">
+        <v>87356501177</v>
+      </c>
+      <c r="L35" s="30">
+        <v>303217247</v>
+      </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="16">
@@ -1633,9 +1647,15 @@
       <c r="G36" s="23">
         <v>8027</v>
       </c>
-      <c r="J36" s="31"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="33"/>
+      <c r="J36" s="31">
+        <v>5270</v>
+      </c>
+      <c r="K36" s="29">
+        <v>303217247</v>
+      </c>
+      <c r="L36" s="33">
+        <v>1075332</v>
+      </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="16">
@@ -1664,12 +1684,16 @@
       <c r="G38" s="23">
         <v>2962</v>
       </c>
-      <c r="J38" s="25" t="e" cm="1">
-        <f t="array" ref="J38">MINVERSE(J34:L36)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K38" s="26"/>
-      <c r="L38" s="27"/>
+      <c r="J38" s="25" cm="1">
+        <f t="array" ref="J38:L40">MINVERSE(J34:L36)</f>
+        <v>0.28481569242061167</v>
+      </c>
+      <c r="K38" s="26">
+        <v>-5.3767436590376639E-6</v>
+      </c>
+      <c r="L38" s="27">
+        <v>1.2028165353721898E-4</v>
+      </c>
     </row>
     <row r="39" spans="2:12" ht="19" x14ac:dyDescent="0.2">
       <c r="B39" s="16">
@@ -1687,9 +1711,15 @@
       <c r="I39" t="s">
         <v>23</v>
       </c>
-      <c r="J39" s="28"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="30"/>
+      <c r="J39" s="28">
+        <v>-5.3767436590376978E-6</v>
+      </c>
+      <c r="K39" s="29">
+        <v>6.400992033967554E-10</v>
+      </c>
+      <c r="L39" s="30">
+        <v>-1.5414186425934374E-7</v>
+      </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" s="16">
@@ -1704,9 +1734,15 @@
       <c r="G40" s="23">
         <v>5603</v>
       </c>
-      <c r="J40" s="31"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="33"/>
+      <c r="J40" s="31">
+        <v>1.2028165353722753E-4</v>
+      </c>
+      <c r="K40" s="32">
+        <v>-1.5414186425934387E-7</v>
+      </c>
+      <c r="L40" s="33">
+        <v>4.3804692331321642E-5</v>
+      </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16">
